--- a/documentation/Check-list.xlsx
+++ b/documentation/Check-list.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="105">
   <si>
     <t xml:space="preserve">Блок</t>
   </si>
@@ -79,37 +79,97 @@
     <t xml:space="preserve">Отказ в авторизации незарегистрированному пользователю</t>
   </si>
   <si>
+    <t xml:space="preserve">Отказ в авторизации с неверным логином</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отказ в авторизации с неверным паролем</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отказ в авторизации с пробелами после введенных валидных логина и пароля</t>
+  </si>
+  <si>
     <t xml:space="preserve">Не пройдено</t>
   </si>
   <si>
-    <t xml:space="preserve">Отказ в авторизации с неверным логином</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Отказ в авторизации с неверным паролем</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Отказ в авторизации с пробелами после введенных валидных логина и пароля</t>
-  </si>
-  <si>
     <t xml:space="preserve">Отказ в авторизации с пробелами перед введенными валидными логином и паролем</t>
   </si>
   <si>
-    <t xml:space="preserve">Навигационная панель</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Переход между страницами Main, News, About через кнопку Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Переход на страницу с цитатами через кнопку OurMission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выход из приложения  по кнопке LogOut</t>
-  </si>
-  <si>
     <t xml:space="preserve">Main</t>
   </si>
   <si>
-    <t xml:space="preserve">Развернуть и скрыть новости на главной странице.</t>
+    <t xml:space="preserve">Отсутствие перехода на страницу Main через кнопку Menu  с главной страницы</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Переход на страницу </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">News через кнопку Menu</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Переход на страницу About, через кнопку Menu</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Переход на страницу с цитатами через кнопку </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">OurMission  с главной страницы.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Выход из приложения </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> по кнопке  LogOut</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Скрыть и развернуть новости на главной странице.</t>
   </si>
   <si>
     <t xml:space="preserve">Переход на страницу News через кнопку All News</t>
@@ -118,7 +178,137 @@
     <t xml:space="preserve">OurMission</t>
   </si>
   <si>
-    <t xml:space="preserve">Свернуть-развернуть цитату </t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Переход на страницу Main</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> через кнопку Menu со страницы OurMission</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Переход на страницу </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">News через кнопку Menu со страницы OurMission</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Переход на страницу About, через кнопку Menu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">со страницы OurMission</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Кнопка </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">OurMission</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> не активна на странице  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">OurMission</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Выход из приложения </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> по кнопке  LogOut со страницы OurMission</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Развернуть и свернуть цитату на странице OurMission</t>
   </si>
   <si>
     <t xml:space="preserve">About</t>
@@ -174,31 +364,118 @@
     <t xml:space="preserve">News </t>
   </si>
   <si>
-    <t xml:space="preserve">Просмотр новостей</t>
+    <t xml:space="preserve">Отсутствие перехода на страницу News через кнопку Menu</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Переход на страницу Main</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> через кнопку Menu со страницы News</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Переход на страницу About, через кнопку Menu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">со страницы News</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Переход на страницу с цитатами через кнопку </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">OurMission  со страницы News.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">Выход из приложения </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> по кнопке  LogOut со страницы News</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Сортировка новостей по дате добавления</t>
   </si>
   <si>
-    <t xml:space="preserve">Фильтрация новостей по выбранной категории из доступных по умолчанию с выбранными датами «от» и «до»</t>
+    <t xml:space="preserve">Фильтрация новостей по выбранной категории из доступных по умолчанию с выбранными датами «от» и «до» </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наличие уведомление об отсутствии новостей из выбранной категории</t>
   </si>
   <si>
     <t xml:space="preserve">Фильтрация новостей по выбранной категории без указания дат</t>
   </si>
   <si>
+    <t xml:space="preserve">Medium</t>
+  </si>
+  <si>
     <t xml:space="preserve">Фильтрация новостей по выбранной категории с только выбранной датой «от»</t>
   </si>
   <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
     <t xml:space="preserve">Фильтрация новостей по выбранной категории с только выбранной датой «до»</t>
   </si>
   <si>
     <t xml:space="preserve">Отмена внесенной информации в фильтре по кнопке «Cancel»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Наличие уведомление об отсутствии новостей из выбранной категории</t>
   </si>
   <si>
     <t xml:space="preserve">Control panel</t>
@@ -352,7 +629,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -406,15 +683,35 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="204"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF4000"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
@@ -488,7 +785,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -553,14 +850,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -573,7 +878,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -581,7 +886,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -589,7 +894,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -653,7 +958,7 @@
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFFF4000"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
@@ -780,14 +1085,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="89.9"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -957,8 +1262,8 @@
       <c r="D10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="14" t="s">
-        <v>19</v>
+      <c r="E10" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>15</v>
@@ -970,7 +1275,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>7</v>
@@ -988,7 +1293,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>7</v>
@@ -1006,13 +1311,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>22</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>19</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>15</v>
@@ -1029,8 +1334,8 @@
       <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>8</v>
+      <c r="E14" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>15</v>
@@ -1044,21 +1349,21 @@
       <c r="E15" s="11"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="17" t="s">
         <v>25</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="14" t="s">
-        <v>19</v>
+      <c r="E16" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>15</v>
@@ -1069,7 +1374,7 @@
       <c r="B17" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="17" t="s">
         <v>26</v>
       </c>
       <c r="D17" s="10" t="s">
@@ -1087,7 +1392,7 @@
       <c r="B18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="17" t="s">
         <v>27</v>
       </c>
       <c r="D18" s="10" t="s">
@@ -1102,537 +1407,516 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
+      <c r="B19" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="16"/>
+      <c r="B20" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="16"/>
+      <c r="B21" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16"/>
+      <c r="B22" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="16"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="16"/>
+      <c r="B25" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="16"/>
+      <c r="B26" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="16"/>
+      <c r="B27" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="16"/>
+      <c r="B28" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="16"/>
+      <c r="B29" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="16"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="16"/>
+      <c r="B32" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="16"/>
+      <c r="B33" s="20" t="n">
         <v>28</v>
       </c>
-      <c r="B20" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="C20" s="13" t="s">
+      <c r="C33" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="16"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="12"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="20" t="n">
         <v>29</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17"/>
-      <c r="B21" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="C21" s="13" t="s">
+      <c r="C35" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="16"/>
+      <c r="B36" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="D21" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
+      <c r="C36" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="16"/>
+      <c r="B37" s="20" t="n">
         <v>31</v>
       </c>
-      <c r="B23" s="18" t="n">
-        <v>18</v>
-      </c>
-      <c r="C23" s="10" t="s">
+      <c r="C37" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="16"/>
+      <c r="B38" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="12"/>
-    </row>
-    <row r="25" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="s">
+      <c r="C38" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="16"/>
+      <c r="B39" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="B25" s="18" t="n">
-        <v>19</v>
-      </c>
-      <c r="C25" s="10" t="s">
+      <c r="C39" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="24"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="16"/>
+      <c r="B40" s="20" t="n">
         <v>34</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17"/>
-      <c r="B26" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="C26" s="10" t="s">
+      <c r="C40" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="12"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="16"/>
+      <c r="B41" s="20" t="n">
         <v>35</v>
       </c>
-      <c r="D26" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17"/>
-      <c r="B27" s="18" t="n">
-        <v>21</v>
-      </c>
-      <c r="C27" s="13" t="s">
+      <c r="C41" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="16"/>
+      <c r="B42" s="20" t="n">
         <v>36</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="12"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
+      <c r="C42" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="16"/>
+      <c r="B43" s="20" t="n">
         <v>37</v>
       </c>
-      <c r="B29" s="18" t="n">
-        <v>22</v>
-      </c>
-      <c r="C29" s="13" t="s">
+      <c r="C43" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="12"/>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="16"/>
+      <c r="B44" s="20" t="n">
         <v>38</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17"/>
-      <c r="B30" s="18" t="n">
-        <v>23</v>
-      </c>
-      <c r="C30" s="13" t="s">
+      <c r="C44" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="12"/>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="16"/>
+      <c r="B45" s="20" t="n">
         <v>39</v>
       </c>
-      <c r="D30" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17"/>
-      <c r="B31" s="18" t="n">
-        <v>24</v>
-      </c>
-      <c r="C31" s="20" t="s">
+      <c r="C45" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="12"/>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="16"/>
+      <c r="B46" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17"/>
-      <c r="B32" s="18" t="n">
-        <v>25</v>
-      </c>
-      <c r="C32" s="21" t="s">
+      <c r="C46" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="12"/>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="16"/>
+      <c r="B47" s="20" t="n">
         <v>41</v>
       </c>
-      <c r="D32" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17"/>
-      <c r="B33" s="18" t="n">
-        <v>26</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" s="22"/>
-    </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="17"/>
-      <c r="B34" s="18" t="n">
-        <v>27</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17"/>
-      <c r="B35" s="18" t="n">
-        <v>28</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="17"/>
-      <c r="B36" s="18" t="n">
-        <v>29</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="12"/>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38" s="18" t="n">
-        <v>30</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="17"/>
-      <c r="B39" s="18" t="n">
-        <v>31</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="17"/>
-      <c r="B40" s="18" t="n">
-        <v>32</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17"/>
-      <c r="B41" s="18" t="n">
-        <v>33</v>
-      </c>
-      <c r="C41" s="13" t="s">
+      <c r="C47" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D41" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17"/>
-      <c r="B42" s="18" t="n">
-        <v>34</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="17"/>
-      <c r="B43" s="18" t="n">
-        <v>35</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="17"/>
-      <c r="B44" s="18" t="n">
-        <v>36</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="17"/>
-      <c r="B45" s="18" t="n">
-        <v>37</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="17"/>
-      <c r="B46" s="18" t="n">
-        <v>38</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="17"/>
-      <c r="B47" s="18" t="n">
-        <v>39</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="D47" s="10" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="E47" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="12" t="s">
-        <v>15</v>
-      </c>
+      <c r="F47" s="12"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="17"/>
-      <c r="B48" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>15</v>
-      </c>
+      <c r="A48" s="16"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="12"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="17"/>
-      <c r="B49" s="18"/>
+      <c r="A49" s="16"/>
+      <c r="B49" s="20"/>
       <c r="C49" s="13"/>
       <c r="D49" s="10"/>
       <c r="E49" s="11"/>
       <c r="F49" s="12"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="18" t="n">
-        <v>41</v>
-      </c>
-      <c r="C50" s="13" t="s">
+      <c r="A50" s="16"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="12"/>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D50" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G50" s="22"/>
-    </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="17"/>
-      <c r="B51" s="18" t="n">
+      <c r="B51" s="20" t="n">
         <v>42</v>
       </c>
       <c r="C51" s="13" t="s">
@@ -1649,596 +1933,547 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="17"/>
-      <c r="B52" s="18" t="n">
+      <c r="A52" s="16"/>
+      <c r="B52" s="20" t="n">
         <v>43</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>59</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="12" t="s">
-        <v>15</v>
-      </c>
+      <c r="F52" s="12"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="17"/>
-      <c r="B53" s="18" t="n">
+      <c r="A53" s="16"/>
+      <c r="B53" s="20" t="n">
         <v>44</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>60</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="12" t="s">
-        <v>15</v>
-      </c>
+      <c r="F53" s="12"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="17"/>
-      <c r="B54" s="18" t="n">
+      <c r="A54" s="16"/>
+      <c r="B54" s="20" t="n">
         <v>45</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>61</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="12" t="s">
-        <v>15</v>
-      </c>
+      <c r="F54" s="12"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="17"/>
-      <c r="B55" s="18" t="n">
+      <c r="A55" s="16"/>
+      <c r="B55" s="20" t="n">
         <v>46</v>
       </c>
       <c r="C55" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" s="12"/>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="16"/>
+      <c r="B56" s="20" t="n">
+        <v>47</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" s="12"/>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="16"/>
+      <c r="B57" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="12"/>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="16"/>
+      <c r="B58" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="C58" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D55" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="17"/>
-      <c r="B56" s="18" t="n">
-        <v>47</v>
-      </c>
-      <c r="C56" s="13" t="s">
+      <c r="D58" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="12"/>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="16"/>
+      <c r="B59" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="C59" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D56" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="17"/>
-      <c r="B57" s="18" t="n">
-        <v>48</v>
-      </c>
-      <c r="C57" s="13" t="s">
+      <c r="D59" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="12"/>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="16"/>
+      <c r="B60" s="20" t="n">
+        <v>51</v>
+      </c>
+      <c r="C60" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D57" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E57" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="17"/>
-      <c r="B58" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="C58" s="13" t="s">
+      <c r="D60" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="12"/>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="16"/>
+      <c r="B61" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="C61" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D58" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="17"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="12"/>
-    </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="24" t="s">
+      <c r="D61" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="12"/>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="16"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="12"/>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B60" s="18" t="n">
-        <v>50</v>
-      </c>
-      <c r="C60" s="13" t="s">
+      <c r="B63" s="20" t="n">
+        <v>53</v>
+      </c>
+      <c r="C63" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D60" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="24"/>
-      <c r="B61" s="18" t="n">
-        <v>51</v>
-      </c>
-      <c r="C61" s="13" t="s">
+      <c r="D63" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63" s="24"/>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="16"/>
+      <c r="B64" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="C64" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D61" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="24"/>
-      <c r="B62" s="18" t="n">
-        <v>52</v>
-      </c>
-      <c r="C62" s="13" t="s">
+      <c r="D64" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="16"/>
+      <c r="B65" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="C65" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D62" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="24"/>
-      <c r="B63" s="18" t="n">
+      <c r="D65" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="E65" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="16"/>
+      <c r="B66" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="C66" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D63" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="24"/>
-      <c r="B64" s="18" t="n">
-        <v>54</v>
-      </c>
-      <c r="C64" s="13" t="s">
+      <c r="D66" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="16"/>
+      <c r="B67" s="20" t="n">
+        <v>57</v>
+      </c>
+      <c r="C67" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D64" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="24"/>
-      <c r="B65" s="18" t="n">
-        <v>55</v>
-      </c>
-      <c r="C65" s="13" t="s">
+      <c r="D67" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="16"/>
+      <c r="B68" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="C68" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D65" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="24"/>
-      <c r="B66" s="18" t="n">
-        <v>56</v>
-      </c>
-      <c r="C66" s="13" t="s">
+      <c r="D68" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="16"/>
+      <c r="B69" s="20" t="n">
+        <v>59</v>
+      </c>
+      <c r="C69" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D66" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="24"/>
-      <c r="B67" s="18" t="n">
-        <v>57</v>
-      </c>
-      <c r="C67" s="13" t="s">
+      <c r="D69" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="16"/>
+      <c r="B70" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="C70" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D67" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="24"/>
-      <c r="B68" s="18" t="n">
-        <v>58</v>
-      </c>
-      <c r="C68" s="13" t="s">
+      <c r="D70" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="16"/>
+      <c r="B71" s="20" t="n">
+        <v>61</v>
+      </c>
+      <c r="C71" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D68" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="24"/>
-      <c r="B69" s="18" t="n">
-        <v>59</v>
-      </c>
-      <c r="C69" s="13" t="s">
+      <c r="D71" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="16"/>
+      <c r="B72" s="20"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="12"/>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="D69" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="24"/>
-      <c r="B70" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="C70" s="10" t="s">
+      <c r="B73" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="C73" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D70" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E70" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G70" s="22"/>
-    </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="24"/>
-      <c r="B71" s="18"/>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="12"/>
-    </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="8" t="s">
+      <c r="D73" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73" s="12"/>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="26"/>
+      <c r="B74" s="20" t="n">
+        <v>63</v>
+      </c>
+      <c r="C74" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B72" s="9" t="n">
-        <v>61</v>
-      </c>
-      <c r="C72" s="10" t="s">
+      <c r="D74" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F74" s="12"/>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="26"/>
+      <c r="B75" s="20" t="n">
+        <v>64</v>
+      </c>
+      <c r="C75" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D72" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9" t="n">
-        <v>62</v>
-      </c>
-      <c r="C73" s="10" t="s">
+      <c r="D75" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F75" s="12"/>
+    </row>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="26"/>
+      <c r="B76" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="C76" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D73" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9" t="n">
-        <v>63</v>
-      </c>
-      <c r="C74" s="10" t="s">
+      <c r="D76" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="12"/>
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="26"/>
+      <c r="B77" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="C77" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D74" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E74" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9" t="n">
-        <v>64</v>
-      </c>
-      <c r="C75" s="10" t="s">
+      <c r="D77" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F77" s="12"/>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="26"/>
+      <c r="B78" s="20" t="n">
+        <v>67</v>
+      </c>
+      <c r="C78" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E75" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9" t="n">
-        <v>65</v>
-      </c>
-      <c r="C76" s="13" t="s">
+      <c r="D78" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F78" s="12"/>
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="26"/>
+      <c r="B79" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="C79" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D76" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9" t="n">
-        <v>66</v>
-      </c>
-      <c r="C77" s="13" t="s">
+      <c r="D79" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F79" s="12"/>
+    </row>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="26"/>
+      <c r="B80" s="20" t="n">
+        <v>69</v>
+      </c>
+      <c r="C80" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D77" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E77" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F77" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9" t="n">
-        <v>67</v>
-      </c>
-      <c r="C78" s="13" t="s">
+      <c r="D80" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" s="12"/>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="26"/>
+      <c r="B81" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="C81" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D78" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E78" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F78" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9" t="n">
-        <v>68</v>
-      </c>
-      <c r="C79" s="13" t="s">
+      <c r="D81" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="12"/>
+    </row>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="26"/>
+      <c r="B82" s="20" t="n">
+        <v>71</v>
+      </c>
+      <c r="C82" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D79" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E79" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="8"/>
-      <c r="B80" s="9" t="n">
-        <v>69</v>
-      </c>
-      <c r="C80" s="13" t="s">
+      <c r="D82" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" s="12"/>
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="26"/>
+      <c r="B83" s="20" t="n">
+        <v>72</v>
+      </c>
+      <c r="C83" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D80" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E80" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F80" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="8"/>
-      <c r="B81" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="C81" s="13" t="s">
+      <c r="D83" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="12"/>
+      <c r="G83" s="24"/>
+    </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="26"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="10"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="12"/>
+    </row>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D81" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E81" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="8"/>
-      <c r="B82" s="9" t="n">
-        <v>71</v>
-      </c>
-      <c r="C82" s="13" t="s">
+      <c r="B85" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="C85" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D82" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E82" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="8"/>
-      <c r="B83" s="9" t="n">
-        <v>72</v>
-      </c>
-      <c r="C83" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E83" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="8"/>
-      <c r="B84" s="9" t="n">
-        <v>73</v>
-      </c>
-      <c r="C84" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E84" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F84" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="8"/>
-      <c r="B85" s="9" t="n">
-        <v>74</v>
-      </c>
-      <c r="C85" s="13" t="s">
-        <v>92</v>
-      </c>
       <c r="D85" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="12" t="s">
+      <c r="E85" s="11" t="s">
         <v>8</v>
       </c>
       <c r="F85" s="12" t="s">
@@ -2248,16 +2483,16 @@
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="8"/>
       <c r="B86" s="9" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="14" t="s">
-        <v>19</v>
+      <c r="E86" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="F86" s="12" t="s">
         <v>9</v>
@@ -2266,10 +2501,10 @@
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="8"/>
       <c r="B87" s="9" t="n">
-        <v>76</v>
-      </c>
-      <c r="C87" s="13" t="s">
-        <v>94</v>
+        <v>75</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>91</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>7</v>
@@ -2283,34 +2518,267 @@
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="8"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="10"/>
-      <c r="E88" s="25"/>
-      <c r="F88" s="12"/>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C91" s="26"/>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C92" s="26"/>
+      <c r="B88" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E88" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F88" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="8"/>
+      <c r="B89" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E89" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="8"/>
+      <c r="B90" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E90" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F90" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="8"/>
+      <c r="B91" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="8"/>
+      <c r="B92" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F92" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="8"/>
+      <c r="B93" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="8"/>
+      <c r="B94" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="8"/>
+      <c r="B95" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="8"/>
+      <c r="B96" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="8"/>
+      <c r="B97" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F97" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="8"/>
+      <c r="B98" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E98" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F98" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="8"/>
+      <c r="B99" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E99" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F99" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="8"/>
+      <c r="B100" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E100" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="8"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="10"/>
+      <c r="D101" s="10"/>
+      <c r="E101" s="27"/>
+      <c r="F101" s="12"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C104" s="28"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C105" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="A29:A37"/>
-    <mergeCell ref="A38:A49"/>
-    <mergeCell ref="A50:A59"/>
-    <mergeCell ref="A60:A71"/>
-    <mergeCell ref="A72:A87"/>
+    <mergeCell ref="A16:A23"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A35:A50"/>
+    <mergeCell ref="A51:A62"/>
+    <mergeCell ref="A63:A72"/>
+    <mergeCell ref="A73:A84"/>
+    <mergeCell ref="A85:A100"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D2:D88" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D2:D101" type="list">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/documentation/Check-list.xlsx
+++ b/documentation/Check-list.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="106">
   <si>
     <t xml:space="preserve">Блок</t>
   </si>
@@ -125,48 +125,10 @@
     <t xml:space="preserve">Переход на страницу About, через кнопку Menu</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">Переход на страницу с цитатами через кнопку </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">OurMission  с главной страницы.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">Выход из приложения </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> по кнопке  LogOut</t>
-    </r>
+    <t xml:space="preserve">Переход на страницу с цитатами через кнопку OurMission  с главной страницы.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выход из приложения  по кнопке  LogOut</t>
   </si>
   <si>
     <t xml:space="preserve">Скрыть и развернуть новости на главной странице.</t>
@@ -286,26 +248,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">Выход из приложения </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> по кнопке  LogOut со страницы OurMission</t>
-    </r>
+    <t xml:space="preserve">Выход из приложения  по кнопке  LogOut со страницы OurMission</t>
   </si>
   <si>
     <t xml:space="preserve">Развернуть и свернуть цитату на странице OurMission</t>
@@ -432,26 +375,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">Выход из приложения </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> по кнопке  LogOut со страницы News</t>
-    </r>
+    <t xml:space="preserve">Выход из приложения  по кнопке  LogOut со страницы News</t>
   </si>
   <si>
     <t xml:space="preserve">Сортировка новостей по дате добавления</t>
@@ -569,6 +493,9 @@
   </si>
   <si>
     <t xml:space="preserve">Не сохранять внесенные изменения по кнопке «Cancel»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Удалить  новость</t>
   </si>
   <si>
     <t xml:space="preserve">Устройство</t>
@@ -629,7 +556,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -692,19 +619,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
@@ -785,7 +699,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -858,10 +772,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -878,15 +788,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -894,7 +800,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1446,7 +1352,7 @@
       <c r="B21" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="18" t="s">
         <v>30</v>
       </c>
       <c r="D21" s="10" t="s">
@@ -1464,7 +1370,7 @@
       <c r="B22" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="10" t="s">
@@ -1489,7 +1395,7 @@
       <c r="A24" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="20" t="n">
+      <c r="B24" s="19" t="n">
         <v>20</v>
       </c>
       <c r="C24" s="17" t="s">
@@ -1507,7 +1413,7 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16"/>
-      <c r="B25" s="20" t="n">
+      <c r="B25" s="19" t="n">
         <v>21</v>
       </c>
       <c r="C25" s="17" t="s">
@@ -1525,7 +1431,7 @@
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16"/>
-      <c r="B26" s="20" t="n">
+      <c r="B26" s="19" t="n">
         <v>22</v>
       </c>
       <c r="C26" s="17" t="s">
@@ -1543,7 +1449,7 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16"/>
-      <c r="B27" s="20" t="n">
+      <c r="B27" s="19" t="n">
         <v>23</v>
       </c>
       <c r="C27" s="17" t="s">
@@ -1561,7 +1467,7 @@
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="16"/>
-      <c r="B28" s="20" t="n">
+      <c r="B28" s="19" t="n">
         <v>24</v>
       </c>
       <c r="C28" s="18" t="s">
@@ -1579,10 +1485,10 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="16"/>
-      <c r="B29" s="20" t="n">
+      <c r="B29" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="18" t="s">
         <v>38</v>
       </c>
       <c r="D29" s="10" t="s">
@@ -1597,7 +1503,7 @@
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="16"/>
-      <c r="B30" s="20"/>
+      <c r="B30" s="19"/>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -1607,7 +1513,7 @@
       <c r="A31" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="20" t="n">
+      <c r="B31" s="19" t="n">
         <v>26</v>
       </c>
       <c r="C31" s="10" t="s">
@@ -1625,7 +1531,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="16"/>
-      <c r="B32" s="20" t="n">
+      <c r="B32" s="19" t="n">
         <v>27</v>
       </c>
       <c r="C32" s="10" t="s">
@@ -1643,7 +1549,7 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16"/>
-      <c r="B33" s="20" t="n">
+      <c r="B33" s="19" t="n">
         <v>28</v>
       </c>
       <c r="C33" s="13" t="s">
@@ -1652,7 +1558,7 @@
       <c r="D33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="20" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="12" t="s">
@@ -1661,7 +1567,7 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16"/>
-      <c r="B34" s="20"/>
+      <c r="B34" s="19"/>
       <c r="C34" s="13"/>
       <c r="D34" s="10"/>
       <c r="E34" s="11"/>
@@ -1671,7 +1577,7 @@
       <c r="A35" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="20" t="n">
+      <c r="B35" s="19" t="n">
         <v>29</v>
       </c>
       <c r="C35" s="17" t="s">
@@ -1689,7 +1595,7 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="16"/>
-      <c r="B36" s="20" t="n">
+      <c r="B36" s="19" t="n">
         <v>30</v>
       </c>
       <c r="C36" s="17" t="s">
@@ -1707,10 +1613,10 @@
     </row>
     <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="16"/>
-      <c r="B37" s="20" t="n">
+      <c r="B37" s="19" t="n">
         <v>31</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="21" t="s">
         <v>46</v>
       </c>
       <c r="D37" s="10" t="s">
@@ -1725,10 +1631,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="16"/>
-      <c r="B38" s="20" t="n">
+      <c r="B38" s="19" t="n">
         <v>32</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="12" t="s">
         <v>47</v>
       </c>
       <c r="D38" s="10" t="s">
@@ -1743,7 +1649,7 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="16"/>
-      <c r="B39" s="20" t="n">
+      <c r="B39" s="19" t="n">
         <v>33</v>
       </c>
       <c r="C39" s="18" t="s">
@@ -1758,11 +1664,11 @@
       <c r="F39" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G39" s="24"/>
+      <c r="G39" s="22"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="16"/>
-      <c r="B40" s="20" t="n">
+      <c r="B40" s="19" t="n">
         <v>34</v>
       </c>
       <c r="C40" s="17" t="s">
@@ -1778,10 +1684,10 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16"/>
-      <c r="B41" s="20" t="n">
+      <c r="B41" s="19" t="n">
         <v>35</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="18" t="s">
         <v>50</v>
       </c>
       <c r="D41" s="10" t="s">
@@ -1794,7 +1700,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16"/>
-      <c r="B42" s="20" t="n">
+      <c r="B42" s="19" t="n">
         <v>36</v>
       </c>
       <c r="C42" s="13" t="s">
@@ -1810,10 +1716,10 @@
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="16"/>
-      <c r="B43" s="20" t="n">
+      <c r="B43" s="19" t="n">
         <v>37</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="C43" s="18" t="s">
         <v>52</v>
       </c>
       <c r="D43" s="10" t="s">
@@ -1826,7 +1732,7 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="16"/>
-      <c r="B44" s="20" t="n">
+      <c r="B44" s="19" t="n">
         <v>38</v>
       </c>
       <c r="C44" s="17" t="s">
@@ -1842,10 +1748,10 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16"/>
-      <c r="B45" s="20" t="n">
+      <c r="B45" s="19" t="n">
         <v>39</v>
       </c>
-      <c r="C45" s="19" t="s">
+      <c r="C45" s="18" t="s">
         <v>55</v>
       </c>
       <c r="D45" s="10" t="s">
@@ -1858,10 +1764,10 @@
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="16"/>
-      <c r="B46" s="20" t="n">
+      <c r="B46" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="C46" s="19" t="s">
+      <c r="C46" s="18" t="s">
         <v>56</v>
       </c>
       <c r="D46" s="10" t="s">
@@ -1874,7 +1780,7 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="16"/>
-      <c r="B47" s="20" t="n">
+      <c r="B47" s="19" t="n">
         <v>41</v>
       </c>
       <c r="C47" s="17" t="s">
@@ -1890,15 +1796,15 @@
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="16"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="19"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="18"/>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
       <c r="F48" s="12"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="16"/>
-      <c r="B49" s="20"/>
+      <c r="B49" s="19"/>
       <c r="C49" s="13"/>
       <c r="D49" s="10"/>
       <c r="E49" s="11"/>
@@ -1906,7 +1812,7 @@
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="16"/>
-      <c r="B50" s="20"/>
+      <c r="B50" s="19"/>
       <c r="C50" s="13"/>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -1916,7 +1822,7 @@
       <c r="A51" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B51" s="20" t="n">
+      <c r="B51" s="19" t="n">
         <v>42</v>
       </c>
       <c r="C51" s="13" t="s">
@@ -1934,7 +1840,7 @@
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="16"/>
-      <c r="B52" s="20" t="n">
+      <c r="B52" s="19" t="n">
         <v>43</v>
       </c>
       <c r="C52" s="13" t="s">
@@ -1950,7 +1856,7 @@
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="16"/>
-      <c r="B53" s="20" t="n">
+      <c r="B53" s="19" t="n">
         <v>44</v>
       </c>
       <c r="C53" s="13" t="s">
@@ -1966,7 +1872,7 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="16"/>
-      <c r="B54" s="20" t="n">
+      <c r="B54" s="19" t="n">
         <v>45</v>
       </c>
       <c r="C54" s="13" t="s">
@@ -1982,7 +1888,7 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="16"/>
-      <c r="B55" s="20" t="n">
+      <c r="B55" s="19" t="n">
         <v>46</v>
       </c>
       <c r="C55" s="13" t="s">
@@ -1998,7 +1904,7 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="16"/>
-      <c r="B56" s="20" t="n">
+      <c r="B56" s="19" t="n">
         <v>47</v>
       </c>
       <c r="C56" s="13" t="s">
@@ -2014,7 +1920,7 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="16"/>
-      <c r="B57" s="20" t="n">
+      <c r="B57" s="19" t="n">
         <v>48</v>
       </c>
       <c r="C57" s="13" t="s">
@@ -2030,7 +1936,7 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="16"/>
-      <c r="B58" s="20" t="n">
+      <c r="B58" s="19" t="n">
         <v>49</v>
       </c>
       <c r="C58" s="13" t="s">
@@ -2046,7 +1952,7 @@
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="16"/>
-      <c r="B59" s="20" t="n">
+      <c r="B59" s="19" t="n">
         <v>50</v>
       </c>
       <c r="C59" s="13" t="s">
@@ -2062,7 +1968,7 @@
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="16"/>
-      <c r="B60" s="20" t="n">
+      <c r="B60" s="19" t="n">
         <v>51</v>
       </c>
       <c r="C60" s="13" t="s">
@@ -2078,7 +1984,7 @@
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="16"/>
-      <c r="B61" s="20" t="n">
+      <c r="B61" s="19" t="n">
         <v>52</v>
       </c>
       <c r="C61" s="13" t="s">
@@ -2094,7 +2000,7 @@
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="16"/>
-      <c r="B62" s="20"/>
+      <c r="B62" s="19"/>
       <c r="C62" s="13"/>
       <c r="D62" s="10"/>
       <c r="E62" s="11"/>
@@ -2104,7 +2010,7 @@
       <c r="A63" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B63" s="20" t="n">
+      <c r="B63" s="19" t="n">
         <v>53</v>
       </c>
       <c r="C63" s="13" t="s">
@@ -2113,17 +2019,17 @@
       <c r="D63" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="25" t="s">
+      <c r="E63" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F63" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G63" s="24"/>
+      <c r="G63" s="22"/>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="16"/>
-      <c r="B64" s="20" t="n">
+      <c r="B64" s="19" t="n">
         <v>54</v>
       </c>
       <c r="C64" s="13" t="s">
@@ -2141,7 +2047,7 @@
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="16"/>
-      <c r="B65" s="20" t="n">
+      <c r="B65" s="19" t="n">
         <v>55</v>
       </c>
       <c r="C65" s="13" t="s">
@@ -2159,7 +2065,7 @@
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="16"/>
-      <c r="B66" s="20" t="n">
+      <c r="B66" s="19" t="n">
         <v>56</v>
       </c>
       <c r="C66" s="13" t="s">
@@ -2177,7 +2083,7 @@
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="16"/>
-      <c r="B67" s="20" t="n">
+      <c r="B67" s="19" t="n">
         <v>57</v>
       </c>
       <c r="C67" s="13" t="s">
@@ -2195,7 +2101,7 @@
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="16"/>
-      <c r="B68" s="20" t="n">
+      <c r="B68" s="19" t="n">
         <v>58</v>
       </c>
       <c r="C68" s="13" t="s">
@@ -2213,7 +2119,7 @@
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="16"/>
-      <c r="B69" s="20" t="n">
+      <c r="B69" s="19" t="n">
         <v>59</v>
       </c>
       <c r="C69" s="13" t="s">
@@ -2231,7 +2137,7 @@
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="16"/>
-      <c r="B70" s="20" t="n">
+      <c r="B70" s="19" t="n">
         <v>60</v>
       </c>
       <c r="C70" s="13" t="s">
@@ -2249,7 +2155,7 @@
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="16"/>
-      <c r="B71" s="20" t="n">
+      <c r="B71" s="19" t="n">
         <v>61</v>
       </c>
       <c r="C71" s="13" t="s">
@@ -2267,17 +2173,17 @@
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="16"/>
-      <c r="B72" s="20"/>
+      <c r="B72" s="19"/>
       <c r="C72" s="13"/>
       <c r="D72" s="10"/>
       <c r="E72" s="11"/>
       <c r="F72" s="12"/>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="26" t="s">
+      <c r="A73" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="B73" s="20" t="n">
+      <c r="B73" s="19" t="n">
         <v>62</v>
       </c>
       <c r="C73" s="13" t="s">
@@ -2292,8 +2198,8 @@
       <c r="F73" s="12"/>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="26"/>
-      <c r="B74" s="20" t="n">
+      <c r="A74" s="24"/>
+      <c r="B74" s="19" t="n">
         <v>63</v>
       </c>
       <c r="C74" s="13" t="s">
@@ -2308,8 +2214,8 @@
       <c r="F74" s="12"/>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="26"/>
-      <c r="B75" s="20" t="n">
+      <c r="A75" s="24"/>
+      <c r="B75" s="19" t="n">
         <v>64</v>
       </c>
       <c r="C75" s="13" t="s">
@@ -2324,8 +2230,8 @@
       <c r="F75" s="12"/>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="26"/>
-      <c r="B76" s="20" t="n">
+      <c r="A76" s="24"/>
+      <c r="B76" s="19" t="n">
         <v>65</v>
       </c>
       <c r="C76" s="13" t="s">
@@ -2340,8 +2246,8 @@
       <c r="F76" s="12"/>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="26"/>
-      <c r="B77" s="20" t="n">
+      <c r="A77" s="24"/>
+      <c r="B77" s="19" t="n">
         <v>66</v>
       </c>
       <c r="C77" s="13" t="s">
@@ -2356,8 +2262,8 @@
       <c r="F77" s="12"/>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="26"/>
-      <c r="B78" s="20" t="n">
+      <c r="A78" s="24"/>
+      <c r="B78" s="19" t="n">
         <v>67</v>
       </c>
       <c r="C78" s="13" t="s">
@@ -2372,8 +2278,8 @@
       <c r="F78" s="12"/>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="26"/>
-      <c r="B79" s="20" t="n">
+      <c r="A79" s="24"/>
+      <c r="B79" s="19" t="n">
         <v>68</v>
       </c>
       <c r="C79" s="13" t="s">
@@ -2388,8 +2294,8 @@
       <c r="F79" s="12"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="26"/>
-      <c r="B80" s="20" t="n">
+      <c r="A80" s="24"/>
+      <c r="B80" s="19" t="n">
         <v>69</v>
       </c>
       <c r="C80" s="13" t="s">
@@ -2404,8 +2310,8 @@
       <c r="F80" s="12"/>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="26"/>
-      <c r="B81" s="20" t="n">
+      <c r="A81" s="24"/>
+      <c r="B81" s="19" t="n">
         <v>40</v>
       </c>
       <c r="C81" s="13" t="s">
@@ -2420,8 +2326,8 @@
       <c r="F81" s="12"/>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="26"/>
-      <c r="B82" s="20" t="n">
+      <c r="A82" s="24"/>
+      <c r="B82" s="19" t="n">
         <v>71</v>
       </c>
       <c r="C82" s="13" t="s">
@@ -2436,8 +2342,8 @@
       <c r="F82" s="12"/>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="26"/>
-      <c r="B83" s="20" t="n">
+      <c r="A83" s="24"/>
+      <c r="B83" s="19" t="n">
         <v>72</v>
       </c>
       <c r="C83" s="10" t="s">
@@ -2450,25 +2356,33 @@
         <v>8</v>
       </c>
       <c r="F83" s="12"/>
-      <c r="G83" s="24"/>
+      <c r="G83" s="22"/>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="26"/>
-      <c r="B84" s="20"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="10"/>
-      <c r="E84" s="11"/>
+      <c r="A84" s="24"/>
+      <c r="B84" s="19" t="n">
+        <v>73</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="F84" s="12"/>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B85" s="9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>7</v>
@@ -2483,10 +2397,10 @@
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="8"/>
       <c r="B86" s="9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>7</v>
@@ -2501,10 +2415,10 @@
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="8"/>
       <c r="B87" s="9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>7</v>
@@ -2519,10 +2433,10 @@
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="8"/>
       <c r="B88" s="9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>7</v>
@@ -2537,10 +2451,10 @@
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="8"/>
       <c r="B89" s="9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>7</v>
@@ -2555,10 +2469,10 @@
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="8"/>
       <c r="B90" s="9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>7</v>
@@ -2573,10 +2487,10 @@
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="8"/>
       <c r="B91" s="9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>7</v>
@@ -2591,10 +2505,10 @@
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="8"/>
       <c r="B92" s="9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>7</v>
@@ -2609,10 +2523,10 @@
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="8"/>
       <c r="B93" s="9" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>7</v>
@@ -2627,10 +2541,10 @@
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="8"/>
       <c r="B94" s="9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>7</v>
@@ -2645,10 +2559,10 @@
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="8"/>
       <c r="B95" s="9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>7</v>
@@ -2663,10 +2577,10 @@
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="8"/>
       <c r="B96" s="9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>7</v>
@@ -2681,10 +2595,10 @@
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="8"/>
       <c r="B97" s="9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>7</v>
@@ -2699,10 +2613,10 @@
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="8"/>
       <c r="B98" s="9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D98" s="10" t="s">
         <v>7</v>
@@ -2717,10 +2631,10 @@
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="8"/>
       <c r="B99" s="9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>7</v>
@@ -2735,10 +2649,10 @@
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="8"/>
       <c r="B100" s="9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>7</v>
@@ -2755,14 +2669,14 @@
       <c r="B101" s="9"/>
       <c r="C101" s="10"/>
       <c r="D101" s="10"/>
-      <c r="E101" s="27"/>
+      <c r="E101" s="25"/>
       <c r="F101" s="12"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C104" s="28"/>
+      <c r="C104" s="26"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C105" s="28"/>
+      <c r="C105" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/documentation/Check-list.xlsx
+++ b/documentation/Check-list.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="106">
   <si>
     <t xml:space="preserve">Блок</t>
   </si>
@@ -307,7 +307,7 @@
     <t xml:space="preserve">News </t>
   </si>
   <si>
-    <t xml:space="preserve">Отсутствие перехода на страницу News через кнопку Menu</t>
+    <t xml:space="preserve">Отсутствие кликабельности кнопки News в Menu на странице новостей</t>
   </si>
   <si>
     <r>
@@ -378,37 +378,37 @@
     <t xml:space="preserve">Выход из приложения  по кнопке  LogOut со страницы News</t>
   </si>
   <si>
+    <t xml:space="preserve">Просмотр новостей на странице</t>
+  </si>
+  <si>
     <t xml:space="preserve">Сортировка новостей по дате добавления</t>
   </si>
   <si>
     <t xml:space="preserve">Фильтрация новостей по выбранной категории из доступных по умолчанию с выбранными датами «от» и «до» </t>
   </si>
   <si>
+    <t xml:space="preserve">Фильтрация новостей по выбранной категории без указания дат</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фильтрация новостей по выбранной категории с только выбранной датой «от»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фильтрация новостей по выбранной категории с только выбранной датой «до»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отмена внесенной информации в фильтре по кнопке «Cancel»</t>
+  </si>
+  <si>
     <t xml:space="preserve">Наличие уведомление об отсутствии новостей из выбранной категории</t>
   </si>
   <si>
-    <t xml:space="preserve">Фильтрация новостей по выбранной категории без указания дат</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Фильтрация новостей по выбранной категории с только выбранной датой «от»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Фильтрация новостей по выбранной категории с только выбранной датой «до»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Отмена внесенной информации в фильтре по кнопке «Cancel»</t>
-  </si>
-  <si>
     <t xml:space="preserve">Control panel</t>
   </si>
   <si>
     <t xml:space="preserve">Переход в контрольную панель по кнопке Control panel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Просмотр новостей на странице</t>
   </si>
   <si>
     <t xml:space="preserve">Сортировка новостей  в Control panel по дате добавления </t>
@@ -728,7 +728,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -745,10 +745,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -786,6 +782,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -991,14 +991,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="89.9"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="16.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1035,7 +1035,7 @@
       <c r="E2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       <c r="E3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="11" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       <c r="E4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       <c r="E5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="11" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
+      <c r="F6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
@@ -1117,7 +1117,7 @@
       <c r="E7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       <c r="B8" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="10" t="s">
@@ -1135,7 +1135,7 @@
       <c r="E8" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       <c r="E9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       <c r="E10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       <c r="B11" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="10" t="s">
@@ -1189,7 +1189,7 @@
       <c r="E11" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       <c r="B12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="10" t="s">
@@ -1207,7 +1207,7 @@
       <c r="E12" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="11" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1216,16 +1216,16 @@
       <c r="B13" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="11" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1234,16 +1234,16 @@
       <c r="B14" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1253,16 +1253,16 @@
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
       <c r="E15" s="11"/>
-      <c r="F15" s="12"/>
+      <c r="F15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="16" t="s">
         <v>25</v>
       </c>
       <c r="D16" s="10" t="s">
@@ -1271,16 +1271,16 @@
       <c r="E16" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16"/>
+      <c r="A17" s="15"/>
       <c r="B17" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D17" s="10" t="s">
@@ -1289,16 +1289,16 @@
       <c r="E17" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16"/>
+      <c r="A18" s="15"/>
       <c r="B18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D18" s="10" t="s">
@@ -1307,16 +1307,16 @@
       <c r="E18" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="10" t="s">
@@ -1325,16 +1325,16 @@
       <c r="E19" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16"/>
+      <c r="A20" s="15"/>
       <c r="B20" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="17" t="s">
         <v>29</v>
       </c>
       <c r="D20" s="10" t="s">
@@ -1343,16 +1343,16 @@
       <c r="E20" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="17" t="s">
         <v>30</v>
       </c>
       <c r="D21" s="10" t="s">
@@ -1361,16 +1361,16 @@
       <c r="E21" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="17" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="10" t="s">
@@ -1379,26 +1379,26 @@
       <c r="E22" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="13"/>
+      <c r="C23" s="12"/>
       <c r="D23" s="10"/>
       <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="19" t="n">
+      <c r="B24" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="16" t="s">
         <v>33</v>
       </c>
       <c r="D24" s="10" t="s">
@@ -1407,16 +1407,16 @@
       <c r="E24" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16"/>
-      <c r="B25" s="19" t="n">
+      <c r="A25" s="15"/>
+      <c r="B25" s="18" t="n">
         <v>21</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="16" t="s">
         <v>34</v>
       </c>
       <c r="D25" s="10" t="s">
@@ -1425,16 +1425,16 @@
       <c r="E25" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16"/>
-      <c r="B26" s="19" t="n">
+      <c r="A26" s="15"/>
+      <c r="B26" s="18" t="n">
         <v>22</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="16" t="s">
         <v>35</v>
       </c>
       <c r="D26" s="10" t="s">
@@ -1443,34 +1443,34 @@
       <c r="E26" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16"/>
-      <c r="B27" s="19" t="n">
+      <c r="A27" s="15"/>
+      <c r="B27" s="18" t="n">
         <v>23</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="16" t="s">
         <v>36</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="12" t="s">
+      <c r="E27" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16"/>
-      <c r="B28" s="19" t="n">
+      <c r="A28" s="15"/>
+      <c r="B28" s="18" t="n">
         <v>24</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="17" t="s">
         <v>37</v>
       </c>
       <c r="D28" s="10" t="s">
@@ -1479,16 +1479,16 @@
       <c r="E28" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="F28" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16"/>
-      <c r="B29" s="19" t="n">
+      <c r="A29" s="15"/>
+      <c r="B29" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="17" t="s">
         <v>38</v>
       </c>
       <c r="D29" s="10" t="s">
@@ -1497,23 +1497,23 @@
       <c r="E29" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="F29" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16"/>
-      <c r="B30" s="19"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="18"/>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
-      <c r="F30" s="12"/>
+      <c r="F30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B31" s="18" t="n">
         <v>26</v>
       </c>
       <c r="C31" s="10" t="s">
@@ -1522,16 +1522,16 @@
       <c r="D31" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="F31" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="16"/>
-      <c r="B32" s="19" t="n">
+      <c r="A32" s="15"/>
+      <c r="B32" s="18" t="n">
         <v>27</v>
       </c>
       <c r="C32" s="10" t="s">
@@ -1540,47 +1540,47 @@
       <c r="D32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16"/>
-      <c r="B33" s="19" t="n">
+      <c r="A33" s="15"/>
+      <c r="B33" s="18" t="n">
         <v>28</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="12" t="s">
         <v>42</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="12" t="s">
+      <c r="E33" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="13"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="12"/>
       <c r="D34" s="10"/>
       <c r="E34" s="11"/>
-      <c r="F34" s="12"/>
+      <c r="F34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="19" t="n">
+      <c r="B35" s="18" t="n">
         <v>29</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="16" t="s">
         <v>44</v>
       </c>
       <c r="D35" s="10" t="s">
@@ -1589,16 +1589,16 @@
       <c r="E35" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F35" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16"/>
-      <c r="B36" s="19" t="n">
+      <c r="A36" s="15"/>
+      <c r="B36" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="16" t="s">
         <v>45</v>
       </c>
       <c r="D36" s="10" t="s">
@@ -1607,34 +1607,34 @@
       <c r="E36" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F36" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16"/>
-      <c r="B37" s="19" t="n">
+      <c r="A37" s="15"/>
+      <c r="B37" s="18" t="n">
         <v>31</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="20" t="s">
         <v>46</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="12" t="s">
+      <c r="E37" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16"/>
-      <c r="B38" s="19" t="n">
+      <c r="A38" s="15"/>
+      <c r="B38" s="18" t="n">
         <v>32</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="21" t="s">
         <v>47</v>
       </c>
       <c r="D38" s="10" t="s">
@@ -1643,16 +1643,16 @@
       <c r="E38" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F38" s="12" t="s">
+      <c r="F38" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="16"/>
-      <c r="B39" s="19" t="n">
+      <c r="A39" s="15"/>
+      <c r="B39" s="18" t="n">
         <v>33</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="17" t="s">
         <v>48</v>
       </c>
       <c r="D39" s="10" t="s">
@@ -1661,17 +1661,17 @@
       <c r="E39" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="F39" s="11" t="s">
         <v>15</v>
       </c>
       <c r="G39" s="22"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="16"/>
-      <c r="B40" s="19" t="n">
+      <c r="A40" s="15"/>
+      <c r="B40" s="18" t="n">
         <v>34</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="16" t="s">
         <v>49</v>
       </c>
       <c r="D40" s="10" t="s">
@@ -1680,14 +1680,16 @@
       <c r="E40" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="12"/>
+      <c r="F40" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="16"/>
-      <c r="B41" s="19" t="n">
+      <c r="A41" s="15"/>
+      <c r="B41" s="18" t="n">
         <v>35</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="16" t="s">
         <v>50</v>
       </c>
       <c r="D41" s="10" t="s">
@@ -1696,14 +1698,16 @@
       <c r="E41" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="12"/>
+      <c r="F41" s="11" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="16"/>
-      <c r="B42" s="19" t="n">
+      <c r="A42" s="15"/>
+      <c r="B42" s="18" t="n">
         <v>36</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="17" t="s">
         <v>51</v>
       </c>
       <c r="D42" s="10" t="s">
@@ -1712,14 +1716,16 @@
       <c r="E42" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F42" s="12"/>
+      <c r="F42" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="16"/>
-      <c r="B43" s="19" t="n">
+      <c r="A43" s="15"/>
+      <c r="B43" s="18" t="n">
         <v>37</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="17" t="s">
         <v>52</v>
       </c>
       <c r="D43" s="10" t="s">
@@ -1728,14 +1734,16 @@
       <c r="E43" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="12"/>
+      <c r="F43" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="16"/>
-      <c r="B44" s="19" t="n">
+      <c r="A44" s="15"/>
+      <c r="B44" s="18" t="n">
         <v>38</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D44" s="10" t="s">
@@ -1744,14 +1752,16 @@
       <c r="E44" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="12"/>
+      <c r="F44" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="16"/>
-      <c r="B45" s="19" t="n">
+      <c r="A45" s="15"/>
+      <c r="B45" s="18" t="n">
         <v>39</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="17" t="s">
         <v>55</v>
       </c>
       <c r="D45" s="10" t="s">
@@ -1760,14 +1770,16 @@
       <c r="E45" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="12"/>
+      <c r="F45" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="16"/>
-      <c r="B46" s="19" t="n">
+      <c r="A46" s="15"/>
+      <c r="B46" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="17" t="s">
         <v>56</v>
       </c>
       <c r="D46" s="10" t="s">
@@ -1776,15 +1788,17 @@
       <c r="E46" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="12"/>
+      <c r="F46" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="16"/>
-      <c r="B47" s="19" t="n">
+      <c r="A47" s="15"/>
+      <c r="B47" s="18" t="n">
         <v>41</v>
       </c>
-      <c r="C47" s="17" t="s">
-        <v>51</v>
+      <c r="C47" s="16" t="s">
+        <v>57</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>7</v>
@@ -1792,41 +1806,43 @@
       <c r="E47" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="12"/>
+      <c r="F47" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="16"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="18"/>
+      <c r="A48" s="15"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="17"/>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
-      <c r="F48" s="12"/>
+      <c r="F48" s="11"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="16"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="13"/>
+      <c r="A49" s="15"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="12"/>
       <c r="D49" s="10"/>
       <c r="E49" s="11"/>
-      <c r="F49" s="12"/>
+      <c r="F49" s="11"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="16"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="13"/>
+      <c r="A50" s="15"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="12"/>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
-      <c r="F50" s="12"/>
+      <c r="F50" s="11"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="19" t="n">
+      <c r="A51" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="18" t="n">
         <v>42</v>
       </c>
-      <c r="C51" s="13" t="s">
-        <v>58</v>
+      <c r="C51" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>7</v>
@@ -1834,17 +1850,17 @@
       <c r="E51" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="16"/>
-      <c r="B52" s="19" t="n">
+      <c r="A52" s="15"/>
+      <c r="B52" s="18" t="n">
         <v>43</v>
       </c>
-      <c r="C52" s="13" t="s">
-        <v>59</v>
+      <c r="C52" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>7</v>
@@ -1852,14 +1868,16 @@
       <c r="E52" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="12"/>
+      <c r="F52" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="16"/>
-      <c r="B53" s="19" t="n">
+      <c r="A53" s="15"/>
+      <c r="B53" s="18" t="n">
         <v>44</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="12" t="s">
         <v>60</v>
       </c>
       <c r="D53" s="10" t="s">
@@ -1868,14 +1886,16 @@
       <c r="E53" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="12"/>
+      <c r="F53" s="11" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="16"/>
-      <c r="B54" s="19" t="n">
+      <c r="A54" s="15"/>
+      <c r="B54" s="18" t="n">
         <v>45</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="12" t="s">
         <v>61</v>
       </c>
       <c r="D54" s="10" t="s">
@@ -1884,14 +1904,16 @@
       <c r="E54" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="12"/>
+      <c r="F54" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="16"/>
-      <c r="B55" s="19" t="n">
+      <c r="A55" s="15"/>
+      <c r="B55" s="18" t="n">
         <v>46</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="12" t="s">
         <v>52</v>
       </c>
       <c r="D55" s="10" t="s">
@@ -1900,14 +1922,16 @@
       <c r="E55" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F55" s="12"/>
+      <c r="F55" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="16"/>
-      <c r="B56" s="19" t="n">
+      <c r="A56" s="15"/>
+      <c r="B56" s="18" t="n">
         <v>47</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="12" t="s">
         <v>54</v>
       </c>
       <c r="D56" s="10" t="s">
@@ -1916,14 +1940,16 @@
       <c r="E56" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F56" s="12"/>
+      <c r="F56" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="16"/>
-      <c r="B57" s="19" t="n">
+      <c r="A57" s="15"/>
+      <c r="B57" s="18" t="n">
         <v>48</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C57" s="12" t="s">
         <v>55</v>
       </c>
       <c r="D57" s="10" t="s">
@@ -1932,14 +1958,16 @@
       <c r="E57" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="12"/>
+      <c r="F57" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="16"/>
-      <c r="B58" s="19" t="n">
+      <c r="A58" s="15"/>
+      <c r="B58" s="18" t="n">
         <v>49</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="12" t="s">
         <v>62</v>
       </c>
       <c r="D58" s="10" t="s">
@@ -1948,14 +1976,16 @@
       <c r="E58" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F58" s="12"/>
+      <c r="F58" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="16"/>
-      <c r="B59" s="19" t="n">
+      <c r="A59" s="15"/>
+      <c r="B59" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="C59" s="12" t="s">
         <v>63</v>
       </c>
       <c r="D59" s="10" t="s">
@@ -1964,14 +1994,16 @@
       <c r="E59" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="12"/>
+      <c r="F59" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="16"/>
-      <c r="B60" s="19" t="n">
+      <c r="A60" s="15"/>
+      <c r="B60" s="18" t="n">
         <v>51</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" s="12" t="s">
         <v>64</v>
       </c>
       <c r="D60" s="10" t="s">
@@ -1980,14 +2012,16 @@
       <c r="E60" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F60" s="12"/>
+      <c r="F60" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="16"/>
-      <c r="B61" s="19" t="n">
+      <c r="A61" s="15"/>
+      <c r="B61" s="18" t="n">
         <v>52</v>
       </c>
-      <c r="C61" s="13" t="s">
+      <c r="C61" s="12" t="s">
         <v>65</v>
       </c>
       <c r="D61" s="10" t="s">
@@ -1996,24 +2030,26 @@
       <c r="E61" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="12"/>
+      <c r="F61" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="16"/>
-      <c r="B62" s="19"/>
-      <c r="C62" s="13"/>
+      <c r="A62" s="15"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="12"/>
       <c r="D62" s="10"/>
       <c r="E62" s="11"/>
-      <c r="F62" s="12"/>
+      <c r="F62" s="11"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="16" t="s">
+      <c r="A63" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B63" s="19" t="n">
+      <c r="B63" s="18" t="n">
         <v>53</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="C63" s="12" t="s">
         <v>67</v>
       </c>
       <c r="D63" s="10" t="s">
@@ -2022,17 +2058,17 @@
       <c r="E63" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="F63" s="12" t="s">
+      <c r="F63" s="11" t="s">
         <v>15</v>
       </c>
       <c r="G63" s="22"/>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="16"/>
-      <c r="B64" s="19" t="n">
+      <c r="A64" s="15"/>
+      <c r="B64" s="18" t="n">
         <v>54</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="12" t="s">
         <v>68</v>
       </c>
       <c r="D64" s="10" t="s">
@@ -2041,16 +2077,16 @@
       <c r="E64" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F64" s="12" t="s">
+      <c r="F64" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="16"/>
-      <c r="B65" s="19" t="n">
+      <c r="A65" s="15"/>
+      <c r="B65" s="18" t="n">
         <v>55</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="12" t="s">
         <v>69</v>
       </c>
       <c r="D65" s="10" t="s">
@@ -2059,16 +2095,16 @@
       <c r="E65" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F65" s="12" t="s">
+      <c r="F65" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="16"/>
-      <c r="B66" s="19" t="n">
+      <c r="A66" s="15"/>
+      <c r="B66" s="18" t="n">
         <v>56</v>
       </c>
-      <c r="C66" s="13" t="s">
+      <c r="C66" s="12" t="s">
         <v>70</v>
       </c>
       <c r="D66" s="10" t="s">
@@ -2077,16 +2113,16 @@
       <c r="E66" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F66" s="12" t="s">
+      <c r="F66" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="16"/>
-      <c r="B67" s="19" t="n">
+      <c r="A67" s="15"/>
+      <c r="B67" s="18" t="n">
         <v>57</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="12" t="s">
         <v>71</v>
       </c>
       <c r="D67" s="10" t="s">
@@ -2095,16 +2131,16 @@
       <c r="E67" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F67" s="12" t="s">
+      <c r="F67" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="16"/>
-      <c r="B68" s="19" t="n">
+      <c r="A68" s="15"/>
+      <c r="B68" s="18" t="n">
         <v>58</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="12" t="s">
         <v>72</v>
       </c>
       <c r="D68" s="10" t="s">
@@ -2113,16 +2149,16 @@
       <c r="E68" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F68" s="12" t="s">
+      <c r="F68" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="16"/>
-      <c r="B69" s="19" t="n">
+      <c r="A69" s="15"/>
+      <c r="B69" s="18" t="n">
         <v>59</v>
       </c>
-      <c r="C69" s="13" t="s">
+      <c r="C69" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D69" s="10" t="s">
@@ -2131,16 +2167,16 @@
       <c r="E69" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F69" s="12" t="s">
+      <c r="F69" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="16"/>
-      <c r="B70" s="19" t="n">
+      <c r="A70" s="15"/>
+      <c r="B70" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="12" t="s">
         <v>74</v>
       </c>
       <c r="D70" s="10" t="s">
@@ -2149,16 +2185,16 @@
       <c r="E70" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F70" s="12" t="s">
+      <c r="F70" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="16"/>
-      <c r="B71" s="19" t="n">
+      <c r="A71" s="15"/>
+      <c r="B71" s="18" t="n">
         <v>61</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="12" t="s">
         <v>75</v>
       </c>
       <c r="D71" s="10" t="s">
@@ -2167,26 +2203,26 @@
       <c r="E71" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F71" s="12" t="s">
+      <c r="F71" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="16"/>
-      <c r="B72" s="19"/>
-      <c r="C72" s="13"/>
+      <c r="A72" s="15"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="12"/>
       <c r="D72" s="10"/>
       <c r="E72" s="11"/>
-      <c r="F72" s="12"/>
+      <c r="F72" s="11"/>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="B73" s="19" t="n">
+      <c r="B73" s="18" t="n">
         <v>62</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C73" s="12" t="s">
         <v>77</v>
       </c>
       <c r="D73" s="10" t="s">
@@ -2195,14 +2231,16 @@
       <c r="E73" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="12"/>
+      <c r="F73" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="24"/>
-      <c r="B74" s="19" t="n">
+      <c r="B74" s="18" t="n">
         <v>63</v>
       </c>
-      <c r="C74" s="13" t="s">
+      <c r="C74" s="12" t="s">
         <v>78</v>
       </c>
       <c r="D74" s="10" t="s">
@@ -2211,14 +2249,16 @@
       <c r="E74" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F74" s="12"/>
+      <c r="F74" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="24"/>
-      <c r="B75" s="19" t="n">
+      <c r="B75" s="18" t="n">
         <v>64</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="C75" s="12" t="s">
         <v>79</v>
       </c>
       <c r="D75" s="10" t="s">
@@ -2227,14 +2267,16 @@
       <c r="E75" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F75" s="12"/>
+      <c r="F75" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="24"/>
-      <c r="B76" s="19" t="n">
+      <c r="B76" s="18" t="n">
         <v>65</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="C76" s="12" t="s">
         <v>80</v>
       </c>
       <c r="D76" s="10" t="s">
@@ -2243,14 +2285,16 @@
       <c r="E76" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F76" s="12"/>
+      <c r="F76" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="24"/>
-      <c r="B77" s="19" t="n">
+      <c r="B77" s="18" t="n">
         <v>66</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="C77" s="12" t="s">
         <v>81</v>
       </c>
       <c r="D77" s="10" t="s">
@@ -2259,14 +2303,16 @@
       <c r="E77" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F77" s="12"/>
+      <c r="F77" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="24"/>
-      <c r="B78" s="19" t="n">
+      <c r="B78" s="18" t="n">
         <v>67</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="C78" s="12" t="s">
         <v>82</v>
       </c>
       <c r="D78" s="10" t="s">
@@ -2275,14 +2321,16 @@
       <c r="E78" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F78" s="12"/>
+      <c r="F78" s="11" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="24"/>
-      <c r="B79" s="19" t="n">
+      <c r="B79" s="18" t="n">
         <v>68</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="C79" s="12" t="s">
         <v>83</v>
       </c>
       <c r="D79" s="10" t="s">
@@ -2291,14 +2339,16 @@
       <c r="E79" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F79" s="12"/>
+      <c r="F79" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="24"/>
-      <c r="B80" s="19" t="n">
+      <c r="B80" s="18" t="n">
         <v>69</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C80" s="12" t="s">
         <v>84</v>
       </c>
       <c r="D80" s="10" t="s">
@@ -2307,14 +2357,16 @@
       <c r="E80" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F80" s="12"/>
+      <c r="F80" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="24"/>
-      <c r="B81" s="19" t="n">
+      <c r="B81" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="12" t="s">
         <v>85</v>
       </c>
       <c r="D81" s="10" t="s">
@@ -2323,14 +2375,16 @@
       <c r="E81" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F81" s="12"/>
+      <c r="F81" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="24"/>
-      <c r="B82" s="19" t="n">
+      <c r="B82" s="18" t="n">
         <v>71</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C82" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D82" s="10" t="s">
@@ -2339,11 +2393,13 @@
       <c r="E82" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F82" s="12"/>
+      <c r="F82" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="24"/>
-      <c r="B83" s="19" t="n">
+      <c r="B83" s="18" t="n">
         <v>72</v>
       </c>
       <c r="C83" s="10" t="s">
@@ -2355,12 +2411,14 @@
       <c r="E83" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="12"/>
+      <c r="F83" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="G83" s="22"/>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="24"/>
-      <c r="B84" s="19" t="n">
+      <c r="B84" s="18" t="n">
         <v>73</v>
       </c>
       <c r="C84" s="10" t="s">
@@ -2372,53 +2430,45 @@
       <c r="E84" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F84" s="12"/>
+      <c r="F84" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="8" t="s">
+      <c r="A85" s="24"/>
+      <c r="B85" s="18"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="10"/>
+      <c r="E85" s="11"/>
+      <c r="F85" s="11"/>
+    </row>
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B85" s="9" t="n">
+      <c r="B86" s="9" t="n">
         <v>74</v>
       </c>
-      <c r="C85" s="10" t="s">
+      <c r="C86" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D85" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E85" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="8"/>
-      <c r="B86" s="9" t="n">
-        <v>75</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>91</v>
-      </c>
       <c r="D86" s="10" t="s">
         <v>7</v>
       </c>
       <c r="E86" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F86" s="12" t="s">
+      <c r="F86" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="8"/>
       <c r="B87" s="9" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>7</v>
@@ -2426,17 +2476,17 @@
       <c r="E87" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F87" s="12" t="s">
+      <c r="F87" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="8"/>
       <c r="B88" s="9" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>7</v>
@@ -2444,17 +2494,17 @@
       <c r="E88" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F88" s="12" t="s">
+      <c r="F88" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="8"/>
       <c r="B89" s="9" t="n">
-        <v>78</v>
-      </c>
-      <c r="C89" s="13" t="s">
-        <v>94</v>
+        <v>77</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>7</v>
@@ -2462,221 +2512,239 @@
       <c r="E89" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F89" s="12" t="s">
+      <c r="F89" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="8"/>
       <c r="B90" s="9" t="n">
-        <v>79</v>
-      </c>
-      <c r="C90" s="13" t="s">
-        <v>95</v>
+        <v>78</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>94</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E90" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F90" s="12" t="s">
+      <c r="E90" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F90" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="8"/>
       <c r="B91" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="C91" s="13" t="s">
-        <v>96</v>
+        <v>79</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>95</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="12" t="s">
+      <c r="E91" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F91" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="8"/>
       <c r="B92" s="9" t="n">
-        <v>81</v>
-      </c>
-      <c r="C92" s="13" t="s">
-        <v>97</v>
+        <v>80</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E92" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" s="12" t="s">
+      <c r="E92" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F92" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="8"/>
       <c r="B93" s="9" t="n">
-        <v>82</v>
-      </c>
-      <c r="C93" s="13" t="s">
-        <v>98</v>
+        <v>81</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>97</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E93" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" s="12" t="s">
+      <c r="E93" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="8"/>
       <c r="B94" s="9" t="n">
-        <v>83</v>
-      </c>
-      <c r="C94" s="13" t="s">
-        <v>99</v>
+        <v>82</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>98</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E94" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="12" t="s">
+      <c r="E94" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="8"/>
       <c r="B95" s="9" t="n">
-        <v>84</v>
-      </c>
-      <c r="C95" s="13" t="s">
-        <v>100</v>
+        <v>83</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E95" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F95" s="12" t="s">
+      <c r="E95" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F95" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="8"/>
       <c r="B96" s="9" t="n">
-        <v>85</v>
-      </c>
-      <c r="C96" s="10" t="s">
-        <v>101</v>
+        <v>84</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>100</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E96" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="12" t="s">
+      <c r="E96" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="8"/>
       <c r="B97" s="9" t="n">
-        <v>86</v>
-      </c>
-      <c r="C97" s="13" t="s">
-        <v>102</v>
+        <v>85</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E97" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F97" s="12" t="s">
+      <c r="E97" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F97" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="8"/>
       <c r="B98" s="9" t="n">
-        <v>87</v>
-      </c>
-      <c r="C98" s="13" t="s">
-        <v>103</v>
+        <v>86</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>102</v>
       </c>
       <c r="D98" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F98" s="12" t="s">
+      <c r="E98" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F98" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="8"/>
       <c r="B99" s="9" t="n">
-        <v>88</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>104</v>
+        <v>87</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E99" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F99" s="12" t="s">
+      <c r="E99" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F99" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="8"/>
       <c r="B100" s="9" t="n">
-        <v>89</v>
-      </c>
-      <c r="C100" s="13" t="s">
-        <v>105</v>
+        <v>88</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>104</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="12" t="s">
+      <c r="E100" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F100" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="8"/>
-      <c r="B101" s="9"/>
-      <c r="C101" s="10"/>
-      <c r="D101" s="10"/>
-      <c r="E101" s="25"/>
-      <c r="F101" s="12"/>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C104" s="26"/>
+      <c r="B101" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E101" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="8"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="10"/>
+      <c r="D102" s="10"/>
+      <c r="E102" s="25"/>
+      <c r="F102" s="11"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C105" s="26"/>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C106" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2689,10 +2757,10 @@
     <mergeCell ref="A51:A62"/>
     <mergeCell ref="A63:A72"/>
     <mergeCell ref="A73:A84"/>
-    <mergeCell ref="A85:A100"/>
+    <mergeCell ref="A86:A101"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D2:D101" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D2:D102" type="list">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
